--- a/Data/EXCEL/Transfer/salemon/20240711/2324-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/2324-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E442327B-A772-4EFC-BB7B-6D0C8FDD4736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEA2B257-60CC-406E-9300-5A86FDC90173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4570" yWindow="2620" windowWidth="18240" windowHeight="13390" xr2:uid="{329B9A2A-AE4F-4752-904E-F9BBF65B1BDB}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{65F62D03-FE6D-4CAF-B449-B2CDDCD27002}"/>
   </bookViews>
   <sheets>
     <sheet name="2324-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1267,23 +1267,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8B9563-68DE-4CB1-9C1F-5FF55D1A3BB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B513572D-7C17-4D4D-8DC4-0CADE3AEEBBF}">
   <dimension ref="A1:Q436"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1310,7 +1310,7 @@
       <c r="P1" s="21"/>
       <c r="Q1" s="22"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="18"/>
       <c r="B2" s="17" t="s">
         <v>4</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Q2" s="22"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -1392,7 +1392,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="19"/>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -1431,7 +1431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>-3.65</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>45413</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>-4.7300000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>-4.03</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>45352</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>-4.72</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>-6.26</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>45292</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>45231</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>-12.3</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>-13.8</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>45170</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>-13.9</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>45108</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>-14.7</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>45047</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>-9.57</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>-10.4</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>44986</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>-21.8</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>-21.4</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>44927</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>-24.1</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>-13.1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>44866</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>-9.67</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>-6.63</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>44805</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>-4.99</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>-2.88</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>44743</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>-1.22</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="11">
         <v>44682</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>-6.48</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>-10.4</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <v>44621</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>-0.79</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>44562</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>-9.35</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>44501</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="11">
         <v>44440</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="11">
         <v>44378</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="11">
         <v>44317</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <v>44256</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>59.8</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="11">
         <v>44197</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="11">
         <v>44136</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="11">
         <v>44075</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="11">
         <v>44013</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>-1.1100000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>-3.73</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="11">
         <v>43952</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>-3.45</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>-5.49</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="11">
         <v>43891</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>-13.6</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>-18.600000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="11">
         <v>43831</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>-11.9</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="11">
         <v>43770</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="11">
         <v>43709</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="11">
         <v>43647</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>6.68</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="11">
         <v>43586</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>9.32</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="11">
         <v>43525</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>7.39</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="11">
         <v>43466</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>9.01</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="11">
         <v>43405</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="11">
         <v>43344</v>
       </c>
@@ -5141,7 +5141,7 @@
         <v>8.6199999999999992</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="11">
         <v>43282</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="11">
         <v>43221</v>
       </c>
@@ -5353,7 +5353,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="11">
         <v>43160</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="11">
         <v>43101</v>
       </c>
@@ -5565,7 +5565,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="11">
         <v>43040</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="11">
         <v>42979</v>
       </c>
@@ -5777,7 +5777,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="11">
         <v>42917</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="11">
         <v>42856</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="11">
         <v>42795</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="11">
         <v>42736</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>-8.56</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>-9.49</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="11">
         <v>42675</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>-9.01</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>-9.01</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="11">
         <v>42614</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>-10.7</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>-9.66</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="11">
         <v>42552</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="11">
         <v>42491</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>-13.8</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6678,7 +6678,7 @@
         <v>-14.2</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="11">
         <v>42430</v>
       </c>
@@ -6731,7 +6731,7 @@
         <v>-10.9</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6784,7 +6784,7 @@
         <v>-13.2</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="11">
         <v>42370</v>
       </c>
@@ -6837,7 +6837,7 @@
         <v>-18.399999999999999</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6890,7 +6890,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="11">
         <v>42309</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="11">
         <v>42248</v>
       </c>
@@ -7049,7 +7049,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7102,7 +7102,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="11">
         <v>42186</v>
       </c>
@@ -7155,7 +7155,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>42156</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>6.63</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="11">
         <v>42125</v>
       </c>
@@ -7261,7 +7261,7 @@
         <v>9.7100000000000009</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>42095</v>
       </c>
@@ -7314,7 +7314,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="11">
         <v>42064</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>42036</v>
       </c>
@@ -7420,7 +7420,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="11">
         <v>42005</v>
       </c>
@@ -7473,7 +7473,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>41974</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="11">
         <v>41944</v>
       </c>
@@ -7579,7 +7579,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>41913</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="11">
         <v>41883</v>
       </c>
@@ -7685,7 +7685,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>41852</v>
       </c>
@@ -7738,7 +7738,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="11">
         <v>41821</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>41791</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="11">
         <v>41760</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>41730</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="11">
         <v>41699</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>41671</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="11">
         <v>41640</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>-6.48</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>41609</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="11">
         <v>41579</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>41548</v>
       </c>
@@ -8268,7 +8268,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="11">
         <v>41518</v>
       </c>
@@ -8321,7 +8321,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>41487</v>
       </c>
@@ -8374,7 +8374,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="11">
         <v>41456</v>
       </c>
@@ -8427,7 +8427,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>41426</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="11">
         <v>41395</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>41365</v>
       </c>
@@ -8586,7 +8586,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="11">
         <v>41334</v>
       </c>
@@ -8639,7 +8639,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>41306</v>
       </c>
@@ -8692,7 +8692,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="11">
         <v>41275</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>41244</v>
       </c>
@@ -8798,7 +8798,7 @@
         <v>-1.37</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" s="11">
         <v>41214</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>-2.74</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>41183</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>-3.63</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" s="11">
         <v>41153</v>
       </c>
@@ -8957,7 +8957,7 @@
         <v>-4.1900000000000004</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>41122</v>
       </c>
@@ -9010,7 +9010,7 @@
         <v>-6.3</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" s="11">
         <v>41091</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>-5.73</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>41061</v>
       </c>
@@ -9116,7 +9116,7 @@
         <v>-6.14</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" s="11">
         <v>41030</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>-8.69</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>41000</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>-8.1199999999999992</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" s="11">
         <v>40969</v>
       </c>
@@ -9275,7 +9275,7 @@
         <v>-5.85</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>40940</v>
       </c>
@@ -9328,7 +9328,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" s="11">
         <v>40909</v>
       </c>
@@ -9381,7 +9381,7 @@
         <v>-21.7</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>40878</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" s="11">
         <v>40848</v>
       </c>
@@ -9487,7 +9487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>40817</v>
       </c>
@@ -9540,7 +9540,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" s="11">
         <v>40787</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>40756</v>
       </c>
@@ -9646,7 +9646,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" s="11">
         <v>40725</v>
       </c>
@@ -9699,7 +9699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>40695</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" s="11">
         <v>40664</v>
       </c>
@@ -9805,7 +9805,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>40634</v>
       </c>
@@ -9858,7 +9858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" s="11">
         <v>40603</v>
       </c>
@@ -9911,7 +9911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>40575</v>
       </c>
@@ -9964,7 +9964,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" s="11">
         <v>40544</v>
       </c>
@@ -10017,7 +10017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>40513</v>
       </c>
@@ -10070,7 +10070,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" s="11">
         <v>40483</v>
       </c>
@@ -10123,7 +10123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>40452</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" s="11">
         <v>40422</v>
       </c>
@@ -10229,7 +10229,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>40391</v>
       </c>
@@ -10282,7 +10282,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" s="11">
         <v>40360</v>
       </c>
@@ -10335,7 +10335,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>40330</v>
       </c>
@@ -10388,7 +10388,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" s="11">
         <v>40299</v>
       </c>
@@ -10441,7 +10441,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>40269</v>
       </c>
@@ -10494,7 +10494,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" s="11">
         <v>40238</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>40210</v>
       </c>
@@ -10600,7 +10600,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" s="11">
         <v>40179</v>
       </c>
@@ -10653,7 +10653,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
         <v>40148</v>
       </c>
@@ -10706,7 +10706,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" s="11">
         <v>40118</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" s="5">
         <v>40087</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" s="11">
         <v>40057</v>
       </c>
@@ -10865,7 +10865,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
         <v>40026</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" s="11">
         <v>39995</v>
       </c>
@@ -10971,7 +10971,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
         <v>39965</v>
       </c>
@@ -11024,7 +11024,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" s="11">
         <v>39934</v>
       </c>
@@ -11077,7 +11077,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" s="5">
         <v>39904</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" s="11">
         <v>39873</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" s="5">
         <v>39845</v>
       </c>
@@ -11236,7 +11236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" s="11">
         <v>39814</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
         <v>39783</v>
       </c>
@@ -11342,7 +11342,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" s="11">
         <v>39753</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
         <v>39722</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" s="11">
         <v>39692</v>
       </c>
@@ -11501,7 +11501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>39661</v>
       </c>
@@ -11554,7 +11554,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" s="11">
         <v>39630</v>
       </c>
@@ -11607,7 +11607,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>39600</v>
       </c>
@@ -11660,7 +11660,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" s="11">
         <v>39569</v>
       </c>
@@ -11713,7 +11713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>39539</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" s="11">
         <v>39508</v>
       </c>
@@ -11819,7 +11819,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
         <v>39479</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" s="11">
         <v>39448</v>
       </c>
@@ -11925,7 +11925,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" s="5">
         <v>39417</v>
       </c>
@@ -11978,7 +11978,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" s="11">
         <v>39387</v>
       </c>
@@ -12031,7 +12031,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>39356</v>
       </c>
@@ -12084,7 +12084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" s="11">
         <v>39326</v>
       </c>
@@ -12137,7 +12137,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>39295</v>
       </c>
@@ -12190,7 +12190,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" s="11">
         <v>39264</v>
       </c>
@@ -12243,7 +12243,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" s="5">
         <v>39234</v>
       </c>
@@ -12296,7 +12296,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" s="11">
         <v>39203</v>
       </c>
@@ -12349,7 +12349,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>39173</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" s="11">
         <v>39142</v>
       </c>
@@ -12455,7 +12455,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
         <v>39114</v>
       </c>
@@ -12508,7 +12508,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" s="11">
         <v>39083</v>
       </c>
@@ -12561,1112 +12561,1112 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" s="11">
         <v>45413</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" s="11">
         <v>45352</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" s="11">
         <v>45292</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" s="11">
         <v>45231</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" s="11">
         <v>45170</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" s="11">
         <v>45108</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" s="11">
         <v>45047</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" s="11">
         <v>44986</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" s="11">
         <v>44927</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" s="11">
         <v>44866</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" s="11">
         <v>44805</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" s="11">
         <v>44743</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A242" s="11">
         <v>44682</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A243" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A244" s="11">
         <v>44621</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A245" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A246" s="11">
         <v>44562</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A247" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A248" s="11">
         <v>44501</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A249" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A250" s="11">
         <v>44440</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A251" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A252" s="11">
         <v>44378</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A254" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A255" s="11">
         <v>44317</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A256" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" s="11">
         <v>44256</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A258" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A259" s="11">
         <v>44197</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A260" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A261" s="11">
         <v>44136</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A262" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A263" s="11">
         <v>44075</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A264" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A265" s="11">
         <v>44013</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A266" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A267" s="11">
         <v>43952</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A268" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A269" s="11">
         <v>43891</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A270" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A271" s="11">
         <v>43831</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A273" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A274" s="11">
         <v>43770</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A275" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A276" s="11">
         <v>43709</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A277" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A278" s="11">
         <v>43647</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A279" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A280" s="11">
         <v>43586</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A281" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A282" s="11">
         <v>43525</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A283" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A284" s="11">
         <v>43466</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A285" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A286" s="11">
         <v>43405</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A287" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A288" s="11">
         <v>43344</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A289" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A290" s="11">
         <v>43282</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A292" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A293" s="11">
         <v>43221</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A294" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A295" s="11">
         <v>43160</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A296" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A297" s="11">
         <v>43101</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A298" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A299" s="11">
         <v>43040</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A300" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A301" s="11">
         <v>42979</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A302" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A303" s="11">
         <v>42917</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A304" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A305" s="11">
         <v>42856</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A306" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A307" s="11">
         <v>42795</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A308" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A309" s="11">
         <v>42736</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A310" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A311" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A312" s="11">
         <v>42675</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A313" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A314" s="11">
         <v>42614</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A315" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A316" s="11">
         <v>42552</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A317" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A318" s="11">
         <v>42491</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A319" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A320" s="11">
         <v>42430</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A321" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A322" s="11">
         <v>42370</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A323" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A324" s="11">
         <v>42309</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A325" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A326" s="11">
         <v>42248</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A327" s="5">
         <v>42217</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A328" s="11">
         <v>42186</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A330" s="5">
         <v>42156</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A331" s="11">
         <v>42125</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A332" s="5">
         <v>42095</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A333" s="11">
         <v>42064</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A334" s="5">
         <v>42036</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A335" s="11">
         <v>42005</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A336" s="5">
         <v>41974</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A337" s="11">
         <v>41944</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A338" s="5">
         <v>41913</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A339" s="11">
         <v>41883</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A340" s="5">
         <v>41852</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A341" s="11">
         <v>41821</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A342" s="5">
         <v>41791</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A343" s="11">
         <v>41760</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A344" s="5">
         <v>41730</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A345" s="11">
         <v>41699</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A346" s="5">
         <v>41671</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A347" s="11">
         <v>41640</v>
       </c>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A349" s="5">
         <v>41609</v>
       </c>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A350" s="11">
         <v>41579</v>
       </c>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A351" s="5">
         <v>41548</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A352" s="11">
         <v>41518</v>
       </c>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A353" s="5">
         <v>41487</v>
       </c>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A354" s="11">
         <v>41456</v>
       </c>
     </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A355" s="5">
         <v>41426</v>
       </c>
     </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A356" s="11">
         <v>41395</v>
       </c>
     </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A357" s="5">
         <v>41365</v>
       </c>
     </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A358" s="11">
         <v>41334</v>
       </c>
     </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A359" s="5">
         <v>41306</v>
       </c>
     </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A360" s="11">
         <v>41275</v>
       </c>
     </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A361" s="5">
         <v>41244</v>
       </c>
     </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A362" s="11">
         <v>41214</v>
       </c>
     </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A363" s="5">
         <v>41183</v>
       </c>
     </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A364" s="11">
         <v>41153</v>
       </c>
     </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A365" s="5">
         <v>41122</v>
       </c>
     </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A366" s="11">
         <v>41091</v>
       </c>
     </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A368" s="5">
         <v>41061</v>
       </c>
     </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A369" s="11">
         <v>41030</v>
       </c>
     </row>
-    <row r="370" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A370" s="5">
         <v>41000</v>
       </c>
     </row>
-    <row r="371" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A371" s="11">
         <v>40969</v>
       </c>
     </row>
-    <row r="372" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A372" s="5">
         <v>40940</v>
       </c>
     </row>
-    <row r="373" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A373" s="11">
         <v>40909</v>
       </c>
     </row>
-    <row r="374" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A374" s="5">
         <v>40878</v>
       </c>
     </row>
-    <row r="375" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A375" s="11">
         <v>40848</v>
       </c>
     </row>
-    <row r="376" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A376" s="5">
         <v>40817</v>
       </c>
     </row>
-    <row r="377" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A377" s="11">
         <v>40787</v>
       </c>
     </row>
-    <row r="378" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A378" s="5">
         <v>40756</v>
       </c>
     </row>
-    <row r="379" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A379" s="11">
         <v>40725</v>
       </c>
     </row>
-    <row r="380" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A380" s="5">
         <v>40695</v>
       </c>
     </row>
-    <row r="381" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A381" s="11">
         <v>40664</v>
       </c>
     </row>
-    <row r="382" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A382" s="5">
         <v>40634</v>
       </c>
     </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A383" s="11">
         <v>40603</v>
       </c>
     </row>
-    <row r="384" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A384" s="5">
         <v>40575</v>
       </c>
     </row>
-    <row r="385" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A385" s="11">
         <v>40544</v>
       </c>
     </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A386" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A387" s="5">
         <v>40513</v>
       </c>
     </row>
-    <row r="388" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A388" s="11">
         <v>40483</v>
       </c>
     </row>
-    <row r="389" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A389" s="5">
         <v>40452</v>
       </c>
     </row>
-    <row r="390" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A390" s="11">
         <v>40422</v>
       </c>
     </row>
-    <row r="391" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A391" s="5">
         <v>40391</v>
       </c>
     </row>
-    <row r="392" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A392" s="11">
         <v>40360</v>
       </c>
     </row>
-    <row r="393" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A393" s="5">
         <v>40330</v>
       </c>
     </row>
-    <row r="394" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A394" s="11">
         <v>40299</v>
       </c>
     </row>
-    <row r="395" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A395" s="5">
         <v>40269</v>
       </c>
     </row>
-    <row r="396" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A396" s="11">
         <v>40238</v>
       </c>
     </row>
-    <row r="397" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A397" s="5">
         <v>40210</v>
       </c>
     </row>
-    <row r="398" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A398" s="11">
         <v>40179</v>
       </c>
     </row>
-    <row r="399" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A399" s="5">
         <v>40148</v>
       </c>
     </row>
-    <row r="400" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A400" s="11">
         <v>40118</v>
       </c>
     </row>
-    <row r="401" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A401" s="5">
         <v>40087</v>
       </c>
     </row>
-    <row r="402" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A402" s="11">
         <v>40057</v>
       </c>
     </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A403" s="5">
         <v>40026</v>
       </c>
     </row>
-    <row r="404" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A404" s="11">
         <v>39995</v>
       </c>
     </row>
-    <row r="405" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A406" s="5">
         <v>39965</v>
       </c>
     </row>
-    <row r="407" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A407" s="11">
         <v>39934</v>
       </c>
     </row>
-    <row r="408" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A408" s="5">
         <v>39904</v>
       </c>
     </row>
-    <row r="409" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A409" s="11">
         <v>39873</v>
       </c>
     </row>
-    <row r="410" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A410" s="5">
         <v>39845</v>
       </c>
     </row>
-    <row r="411" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A411" s="11">
         <v>39814</v>
       </c>
     </row>
-    <row r="412" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A412" s="5">
         <v>39783</v>
       </c>
     </row>
-    <row r="413" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A413" s="11">
         <v>39753</v>
       </c>
     </row>
-    <row r="414" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A414" s="5">
         <v>39722</v>
       </c>
     </row>
-    <row r="415" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A415" s="11">
         <v>39692</v>
       </c>
     </row>
-    <row r="416" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A416" s="5">
         <v>39661</v>
       </c>
     </row>
-    <row r="417" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A417" s="11">
         <v>39630</v>
       </c>
     </row>
-    <row r="418" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A418" s="5">
         <v>39600</v>
       </c>
     </row>
-    <row r="419" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A419" s="11">
         <v>39569</v>
       </c>
     </row>
-    <row r="420" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A420" s="5">
         <v>39539</v>
       </c>
     </row>
-    <row r="421" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A421" s="11">
         <v>39508</v>
       </c>
     </row>
-    <row r="422" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A422" s="5">
         <v>39479</v>
       </c>
     </row>
-    <row r="423" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A423" s="11">
         <v>39448</v>
       </c>
     </row>
-    <row r="424" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A425" s="5">
         <v>39417</v>
       </c>
     </row>
-    <row r="426" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A426" s="11">
         <v>39387</v>
       </c>
     </row>
-    <row r="427" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A427" s="5">
         <v>39356</v>
       </c>
     </row>
-    <row r="428" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A428" s="11">
         <v>39326</v>
       </c>
     </row>
-    <row r="429" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A429" s="5">
         <v>39295</v>
       </c>
     </row>
-    <row r="430" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A430" s="11">
         <v>39264</v>
       </c>
     </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A431" s="5">
         <v>39234</v>
       </c>
     </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A432" s="11">
         <v>39203</v>
       </c>
     </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A433" s="5">
         <v>39173</v>
       </c>
     </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A434" s="11">
         <v>39142</v>
       </c>
     </row>
-    <row r="435" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A435" s="5">
         <v>39114</v>
       </c>
     </row>
-    <row r="436" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A436" s="11">
         <v>39083</v>
       </c>
